--- a/outputs/Book1_report.xlsx
+++ b/outputs/Book1_report.xlsx
@@ -7,10 +7,10 @@
   </bookViews>
   <sheets>
     <sheet name="ProjectManagerLevel" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Licence Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Allocated" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Required" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Keystore" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Keystore" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Licence Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Allocated" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Required" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="ISL" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
@@ -1168,6 +1168,123 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>🔑  Keystore</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Key ID</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Autocad</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>sp3d</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>pp</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>KEY_001</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Autocad</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>sp3d</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>el</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>KEY_005</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>User Input</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="8" customHeight="1">
+      <c r="A5" s="12" t="inlineStr"/>
+      <c r="B5" s="12" t="inlineStr"/>
+      <c r="C5" s="12" t="inlineStr"/>
+      <c r="D5" s="12" t="inlineStr"/>
+      <c r="E5" s="12" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1286,7 +1403,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1337,13 +1454,9 @@
           <t>NPP</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>EL + PP</t>
-        </is>
-      </c>
+      <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="6" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -1354,7 +1467,7 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>PP + PL - Own</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
@@ -1364,16 +1477,16 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Valdel</t>
+          <t>Advent</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Sum of all Valdel values</t>
+          <t>User_input</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -1388,122 +1501,13 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" ht="8" customHeight="1">
       <c r="A8" s="12" t="inlineStr"/>
       <c r="B8" s="12" t="inlineStr"/>
       <c r="C8" s="12" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>🔢  Required Licences</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>Autocad — sp3d  |  Order: 22.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Valdel</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="C4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="C5" s="11" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>CEC</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>VEC</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="C7" s="11" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" ht="8" customHeight="1">
-      <c r="A9" s="12" t="inlineStr"/>
-      <c r="B9" s="12" t="inlineStr"/>
-      <c r="C9" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1520,112 +1524,115 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>🔑  Keystore</t>
+          <t>🔢  Required Licences</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Developer</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Key ID</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Autocad — sp3d  |  Order: 22.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Autocad</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>sp3d</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>pp</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>KEY_001</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="n">
+      <c r="C3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Valdel</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="C4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C5" s="11" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>VEC</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="C7" s="11" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Advent</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Autocad</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>sp3d</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>el</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>KEY_005</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>User Input</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="8" customHeight="1">
-      <c r="A5" s="12" t="inlineStr"/>
-      <c r="B5" s="12" t="inlineStr"/>
-      <c r="C5" s="12" t="inlineStr"/>
-      <c r="D5" s="12" t="inlineStr"/>
-      <c r="E5" s="12" t="inlineStr"/>
+      <c r="C8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" ht="8" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="B10" s="12" t="inlineStr"/>
+      <c r="C10" s="12" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
